--- a/cases/dice-roll/published/Dice Roll - Data.xlsx
+++ b/cases/dice-roll/published/Dice Roll - Data.xlsx
@@ -478,6 +478,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -485,6 +486,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -602,6 +604,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1023,6 +1026,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1134,6 +1138,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1259,6 +1264,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
